--- a/predictions/20260913/騎手運勢2026.09.12.xlsx
+++ b/predictions/20260913/騎手運勢2026.09.12.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E4A7AE2-643D-43E4-AFBB-C6616EEC995B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{944E533B-0740-4006-808A-CBF049983611}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4654" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4654" uniqueCount="309">
   <si>
     <t>青字：回収率の高い騎手（妙味度、利益度）</t>
   </si>
@@ -1105,8 +1105,26 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
+    <t>103丸田（重芝・ﾀﾞ◎、外枠、未勝利110、OP156、札・小✖）、99松山（ﾀ102、芝95、新・福・中山✖）
+117国分恭（福・新・小・京都○、芝ダ重○）、96小幡育（阪354・福・函、ダ重145）、91江田照（札197、函495、中山108、中京118、芝重118、未108）、
+101石橋脩（京106、東102、福101、新100、未○、ダ重118、1～3勝105、重賞105）、96国分優（ﾀﾞ・新・未）、92今村聖奈（中山140、札110、京131）、
+86永島まなみ（福・新○）、91土田（芝・札・福・中京○、短）、83水沼（短・東・中山・新馬○）、Sフォーリー、キングスコート、大江原（女）、ブノワ、渡辺竜、プーシャン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>96小林凌（ダ、短・新・1～3勝、東・中山・中京・小）、107太宰(短距離○、重◎、中京・京○）、100石川（中京123、中山110、阪111ダ104）
+104泉谷（小130、福124、中京116、ダ重117）、、105田口（ダ・小・阪）、111高杉、モレイラ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>102横山和（新潟85）、105菊沢（函・阪・小✖、ダ重124）、108松若（短距離102、ﾀ重110、福・東・中山✖）、
+99佐々木（芝・ダ重○）、99小林美駒（ダ重108、福・中山○）、84河原田菜々（中京、福、ダ重○）、97吉田豊（芝重115、左102、長距離103）、
+97川端（短ダ、中京）、104長浜、ピヒューレック、102上里、ハマーハ、イーガン、115森田誠也</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
     <t>100加藤祥、102丹内（阪・東・中京・福島✖）、100三浦（ﾀﾞ104、新馬102、未108）、105長岡禎（札・凾・新・中京・小○、短）、
-111鷲頭虎太（芝ﾀﾞ重○、未111、新・東・京都○）、104小崎（芝・中・長距離）、83大久保、115森田誠也、
+111鷲頭虎太（芝ﾀﾞ重○、未111、新・東・京都○）、104小崎（芝・中・長距離）、83大久保
 96和田竜（新馬113、外枠、重芝104）、93柴田大（新馬、東86）、90柴田未来、97石田拓郎（ダ短逃げ）、90柴田裕一郎、99和田陽希、バルザ、ムーア、スミオン,ミシェル</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -2092,7 +2110,7 @@
         <v>16</v>
       </c>
       <c r="D7" s="59" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.15">
@@ -2146,7 +2164,7 @@
         <v>16</v>
       </c>
       <c r="D11" s="59" t="s">
-        <v>24</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.15">
@@ -2270,7 +2288,7 @@
         <v>4</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>41</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -2312,7 +2330,7 @@
         <v>4</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>47</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
@@ -13184,7 +13202,7 @@
         <v>5</v>
       </c>
       <c r="D7" s="59" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="33.6" customHeight="1" x14ac:dyDescent="0.15">
@@ -13238,7 +13256,7 @@
         <v>4</v>
       </c>
       <c r="D11" s="59" t="s">
-        <v>24</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="33" customHeight="1" x14ac:dyDescent="0.15">
@@ -13362,7 +13380,7 @@
         <v>16</v>
       </c>
       <c r="D20" s="59" t="s">
-        <v>41</v>
+        <v>305</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="12.95" customHeight="1" x14ac:dyDescent="0.15">
@@ -13404,7 +13422,7 @@
         <v>5</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>47</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="23.1" customHeight="1" x14ac:dyDescent="0.15">
